--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
@@ -139,19 +139,19 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="F2:F6">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" sqref="G2:G6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="G2:G6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" sqref="H2:H6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="H2:H6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" sqref="I2:I6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="I2:I6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" sqref="J2:J6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" prompt="Time as HH:mm:ss" sqref="J2:J6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
@@ -11,7 +11,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss z"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss zzz"/>
     <numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
     <numFmt numFmtId="167" formatCode="HH:mm:ss"/>
   </numFmts>
@@ -143,7 +143,7 @@
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="H2:H6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss zzz" prompt="Date and time as yyyy-MM-dd HH:mm:ss zzz" sqref="H2:H6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateAllTypesOptional.verified.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="AllTypes">
     <column index="1" property="Text"/>
     <column index="2" property="Integer"/>
